--- a/data/trans_orig/AIRE_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023</t>
+          <t>Población según los motivos por los que no pagaría para realizar actuaciones que reduzcan la contaminación ambiental en su municipio o lugar de residencia en 2023 (tasa de respuesta: 99,12%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8362</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26700</t>
+          <t>25377</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7962</t>
+          <t>8291</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18580</t>
+          <t>18511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19927</t>
+          <t>19622</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39586</t>
+          <t>39949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>6846</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27072</t>
+          <t>29234</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8127</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23063</t>
+          <t>22061</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>16762</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39996</t>
+          <t>42001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,36%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>66705</t>
+          <t>64957</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93395</t>
+          <t>93112</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>37,34%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,68%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58143</t>
+          <t>57484</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>78158</t>
+          <t>76262</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,97%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>55,7%</t>
+          <t>54,35%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>128163</t>
+          <t>129217</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>163182</t>
+          <t>163380</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>51,98%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>24083</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45543</t>
+          <t>46462</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,18%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17672</t>
+          <t>17842</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32560</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>46785</t>
+          <t>47125</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>74254</t>
+          <t>73615</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,42%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>22418</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43700</t>
+          <t>43619</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16222</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29607</t>
+          <t>29660</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43200</t>
+          <t>43540</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69516</t>
+          <t>68651</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13967</t>
+          <t>13515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>38451</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4892</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17757</t>
+          <t>17402</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21822</t>
+          <t>22022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48565</t>
+          <t>48735</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>9528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26604</t>
+          <t>26379</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13152</t>
+          <t>13453</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>26751</t>
+          <t>27214</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26630</t>
+          <t>26477</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48411</t>
+          <t>47816</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,32%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,94%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69358</t>
+          <t>69517</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>96657</t>
+          <t>97444</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51537</t>
+          <t>51369</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71909</t>
+          <t>71523</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,9%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>50,08%</t>
+          <t>49,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126692</t>
+          <t>126752</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160393</t>
+          <t>160047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>39,61%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,13%</t>
+          <t>50,02%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>29097</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50958</t>
+          <t>51383</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>29,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>23662</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>40758</t>
+          <t>39976</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57970</t>
+          <t>57611</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>84828</t>
+          <t>85073</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,59%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>8446</t>
+          <t>9031</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21797</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16740</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>31380</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,66%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28726</t>
+          <t>28370</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47922</t>
+          <t>47010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2572</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15065</t>
+          <t>13235</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1577</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8124</t>
+          <t>8108</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5583</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18637</t>
+          <t>18868</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30770</t>
+          <t>30841</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>51690</t>
+          <t>52512</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>12966</t>
+          <t>13072</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24487</t>
+          <t>25061</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47615</t>
+          <t>47384</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>71326</t>
+          <t>70927</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,34%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>66781</t>
+          <t>65210</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>92639</t>
+          <t>90682</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>51,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16650</t>
+          <t>16361</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28014</t>
+          <t>27286</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,34%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,63%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86629</t>
+          <t>86490</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113488</t>
+          <t>113783</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>46,94%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20287</t>
+          <t>21257</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>40096</t>
+          <t>41742</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5668</t>
+          <t>5458</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14167</t>
+          <t>14227</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>29111</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>49957</t>
+          <t>50413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,85%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14800</t>
+          <t>14720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>30323</t>
+          <t>29963</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,23%</t>
+          <t>17,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>27,52%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24949</t>
+          <t>25881</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44113</t>
+          <t>44598</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26929</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61260</t>
+          <t>61909</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7451</t>
+          <t>6951</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>43456</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33693</t>
+          <t>29351</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>93243</t>
+          <t>95822</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2889,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>90810</t>
+          <t>92870</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>130290</t>
+          <t>129674</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2904,12 +2904,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2924,12 +2924,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>152124</t>
+          <t>149455</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>421377</t>
+          <t>419092</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,99%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,84%</t>
+          <t>85,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2959,12 +2959,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>248955</t>
+          <t>251191</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>640283</t>
+          <t>665564</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>74,11%</t>
         </is>
       </c>
     </row>
@@ -3002,12 +3002,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133875</t>
+          <t>134675</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>177599</t>
+          <t>176339</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3017,12 +3017,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>32,88%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,62%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37454</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>186087</t>
+          <t>184942</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,91%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>133428</t>
+          <t>123568</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>346450</t>
+          <t>345122</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3087,12 +3087,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>38,43%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>46236</t>
+          <t>47390</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>74287</t>
+          <t>76108</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12705</t>
+          <t>12912</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72803</t>
+          <t>75734</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>51974</t>
+          <t>48388</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>138987</t>
+          <t>139208</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,5%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31311</t>
+          <t>31508</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>55527</t>
+          <t>58561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7621</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>48468</t>
+          <t>49197</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>32936</t>
+          <t>33429</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96924</t>
+          <t>94803</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,56%</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2793</t>
+          <t>2642</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14280</t>
+          <t>14399</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3473,12 +3473,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>16065</t>
+          <t>15701</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30788</t>
+          <t>30161</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3508,12 +3508,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>20758</t>
+          <t>21725</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>38536</t>
+          <t>39744</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3543,12 +3543,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,11%</t>
+          <t>8,36%</t>
         </is>
       </c>
     </row>
@@ -3571,12 +3571,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>66485</t>
+          <t>67248</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>94672</t>
+          <t>94500</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,91%</t>
+          <t>36,32%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,13%</t>
+          <t>51,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3606,12 +3606,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106250</t>
+          <t>106494</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>132602</t>
+          <t>133237</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3621,47 +3621,47 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>36,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
+          <t>45,91%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>197887</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>179574</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>217211</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>41,63%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>37,78%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>45,69%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>197887</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>178553</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>218027</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>41,63%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>37,56%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>45,86%</t>
         </is>
       </c>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48106</t>
+          <t>48626</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>73438</t>
+          <t>73971</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3699,12 +3699,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>26,26%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3719,12 +3719,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65833</t>
+          <t>65831</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>90064</t>
+          <t>89681</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,7 +3739,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3754,12 +3754,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>121239</t>
+          <t>120891</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>156564</t>
+          <t>155523</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3769,12 +3769,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,72%</t>
         </is>
       </c>
     </row>
@@ -3797,12 +3797,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10753</t>
+          <t>10256</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>26942</t>
+          <t>25908</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3812,12 +3812,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3832,12 +3832,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30025</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>49124</t>
+          <t>49328</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3847,12 +3847,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,35%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>16,93%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45620</t>
+          <t>45226</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>70631</t>
+          <t>69377</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3882,12 +3882,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,59%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13361</t>
+          <t>13194</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29662</t>
+          <t>28987</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>24856</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>42069</t>
+          <t>41774</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43181</t>
+          <t>43378</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>67189</t>
+          <t>67069</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -4140,12 +4140,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8810</t>
+          <t>8380</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>37973</t>
+          <t>37317</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4175,12 +4175,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22254</t>
+          <t>22193</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>45972</t>
+          <t>43575</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4190,12 +4190,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4210,12 +4210,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>36643</t>
+          <t>35692</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>77664</t>
+          <t>80629</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4225,12 +4225,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,04%</t>
+          <t>20,81%</t>
         </is>
       </c>
     </row>
@@ -4253,12 +4253,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11251</t>
+          <t>11448</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>35398</t>
+          <t>36588</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4268,12 +4268,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>52,48%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4288,12 +4288,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>100389</t>
+          <t>99765</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>130055</t>
+          <t>130940</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4303,12 +4303,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,37%</t>
+          <t>31,18%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,92%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>116274</t>
+          <t>118770</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>156417</t>
+          <t>158069</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4338,12 +4338,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,01%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,8%</t>
         </is>
       </c>
     </row>
@@ -4366,12 +4366,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>3508</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>19830</t>
+          <t>20675</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4381,12 +4381,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>29,4%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4401,12 +4401,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68398</t>
+          <t>68432</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>97593</t>
+          <t>98533</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>75092</t>
+          <t>76292</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>109951</t>
+          <t>111347</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4451,12 +4451,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -4479,12 +4479,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3040</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20511</t>
+          <t>20735</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4494,12 +4494,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4514,12 +4514,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>32586</t>
+          <t>32170</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>51912</t>
+          <t>51816</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4529,12 +4529,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4549,12 +4549,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>38280</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>65133</t>
+          <t>64908</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4564,12 +4564,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1190</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>15511</t>
+          <t>14347</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4607,12 +4607,12 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39435</t>
+          <t>39531</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>64490</t>
+          <t>63427</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>43680</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>69545</t>
+          <t>70245</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,13%</t>
         </is>
       </c>
     </row>
@@ -4822,12 +4822,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>89074</t>
+          <t>89258</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>152721</t>
+          <t>151425</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4837,12 +4837,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4857,12 +4857,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>63532</t>
+          <t>63160</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>128466</t>
+          <t>127839</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4892,12 +4892,12 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>168870</t>
+          <t>166661</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>268279</t>
+          <t>259165</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,83%</t>
         </is>
       </c>
     </row>
@@ -4935,12 +4935,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>250748</t>
+          <t>247667</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>315466</t>
+          <t>309400</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4950,12 +4950,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>430145</t>
+          <t>428221</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>906359</t>
+          <t>905518</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>62,42%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>695813</t>
+          <t>696176</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1302787</t>
+          <t>1288960</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>48,88%</t>
         </is>
       </c>
     </row>
@@ -5048,12 +5048,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>428162</t>
+          <t>429440</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>502745</t>
+          <t>502960</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5063,12 +5063,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>36,09%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>42,38%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>259068</t>
+          <t>267973</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>493005</t>
+          <t>490885</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,98%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>664478</t>
+          <t>661342</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>970994</t>
+          <t>970404</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -5161,12 +5161,12 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>166829</t>
+          <t>165392</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>221157</t>
+          <t>218665</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5176,12 +5176,12 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>113300</t>
+          <t>103689</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>222502</t>
+          <t>223399</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>287827</t>
+          <t>300443</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>427275</t>
+          <t>423671</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,07%</t>
         </is>
       </c>
     </row>
@@ -5274,12 +5274,12 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>114910</t>
+          <t>117249</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>158089</t>
+          <t>161396</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5289,12 +5289,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>106556</t>
+          <t>102279</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>202196</t>
+          <t>202776</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5324,12 +5324,12 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>234455</t>
+          <t>233733</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>341603</t>
+          <t>342775</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -5359,12 +5359,12 @@
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_2-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>15363</t>
+          <t>15913</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>9071</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25377</t>
+          <t>26941</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>12619</t>
+          <t>14452</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>8291</t>
+          <t>9472</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>18511</t>
+          <t>20928</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>27982</t>
+          <t>30365</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>19622</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>39949</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>12728</t>
+          <t>14708</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6846</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>27900</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>15480</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7880</t>
+          <t>9175</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>22061</t>
+          <t>23781</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>26332</t>
+          <t>30187</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16762</t>
+          <t>20205</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>42001</t>
+          <t>43720</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>12,99%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>79541</t>
+          <t>83734</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>64957</t>
+          <t>69549</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>93112</t>
+          <t>97403</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>37,34%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>52,97%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>67338</t>
+          <t>71348</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>57484</t>
+          <t>61359</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76262</t>
+          <t>82873</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>46,71%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>146879</t>
+          <t>155082</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>129217</t>
+          <t>138045</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>163380</t>
+          <t>173266</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>46,73%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,47%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>34602</t>
+          <t>35208</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24083</t>
+          <t>24827</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46462</t>
+          <t>47961</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24371</t>
+          <t>27031</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>19631</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32170</t>
+          <t>35813</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,93%</t>
+          <t>23,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>58973</t>
+          <t>62238</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>47125</t>
+          <t>49226</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73615</t>
+          <t>76415</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>31746</t>
+          <t>34307</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>22418</t>
+          <t>24632</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>43619</t>
+          <t>45553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>24447</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>17781</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29660</t>
+          <t>32132</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>54122</t>
+          <t>58754</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>43540</t>
+          <t>47169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68651</t>
+          <t>73630</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>21,87%</t>
         </is>
       </c>
     </row>
@@ -1290,17 +1290,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>173981</t>
+          <t>183870</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>173981</t>
+          <t>183870</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>173981</t>
+          <t>183870</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1325,17 +1325,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>140307</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>140307</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>140307</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>314288</t>
+          <t>336627</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>314288</t>
+          <t>336627</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>314288</t>
+          <t>336627</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>22917</t>
+          <t>21761</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13515</t>
+          <t>12825</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38451</t>
+          <t>34537</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9926</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>6665</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17402</t>
+          <t>20833</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>32843</t>
+          <t>33965</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22022</t>
+          <t>23586</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>48735</t>
+          <t>49641</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,56%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16102</t>
+          <t>16535</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>10238</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26379</t>
+          <t>27260</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>19104</t>
+          <t>21184</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13453</t>
+          <t>14495</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>28776</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>35207</t>
+          <t>37719</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>26477</t>
+          <t>27986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>47816</t>
+          <t>49519</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>14,52%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>83045</t>
+          <t>88061</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>69517</t>
+          <t>74232</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97444</t>
+          <t>103051</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47,08%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60603</t>
+          <t>64725</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>51369</t>
+          <t>54290</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>71523</t>
+          <t>75242</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>49,82%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>143648</t>
+          <t>152786</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>126752</t>
+          <t>136022</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>160047</t>
+          <t>171911</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>44,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,89%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39886</t>
+          <t>41738</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29097</t>
+          <t>31147</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51383</t>
+          <t>54113</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>31213</t>
+          <t>33080</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>22910</t>
+          <t>24717</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39976</t>
+          <t>43315</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15,96%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>71099</t>
+          <t>74818</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>57611</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>85073</t>
+          <t>89912</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>14449</t>
+          <t>15565</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9031</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21965</t>
+          <t>24644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>22728</t>
+          <t>26168</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>18526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>31380</t>
+          <t>36140</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>16,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>37177</t>
+          <t>41734</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>28370</t>
+          <t>32347</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>47010</t>
+          <t>53208</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,6%</t>
         </is>
       </c>
     </row>
@@ -1972,17 +1972,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>176399</t>
+          <t>183660</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>176399</t>
+          <t>183660</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>176399</t>
+          <t>183660</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2007,17 +2007,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>143574</t>
+          <t>157362</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>143574</t>
+          <t>157362</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>143574</t>
+          <t>157362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>319973</t>
+          <t>341022</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>319973</t>
+          <t>341022</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>319973</t>
+          <t>341022</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6826</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2572</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>13235</t>
+          <t>15600</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3997</t>
+          <t>4138</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1468</t>
+          <t>1609</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8434</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10601</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5554</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18868</t>
+          <t>19112</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,02%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40423</t>
+          <t>48128</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30841</t>
+          <t>37374</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>52512</t>
+          <t>61908</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>17,52%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>21924</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>16309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25061</t>
+          <t>28926</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,14%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>58804</t>
+          <t>70052</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>47384</t>
+          <t>58156</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70927</t>
+          <t>85741</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>78153</t>
+          <t>85210</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>65210</t>
+          <t>70204</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>90682</t>
+          <t>100003</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,51%</t>
+          <t>50,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>25075</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>16361</t>
+          <t>19223</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,54%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,53%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>99636</t>
+          <t>110285</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>86490</t>
+          <t>93688</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>113783</t>
+          <t>126307</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>41,22%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,41%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>29334</t>
+          <t>32595</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21257</t>
+          <t>23299</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>41742</t>
+          <t>46248</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9231</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>6075</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,05%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>38566</t>
+          <t>42682</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29111</t>
+          <t>31806</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>50413</t>
+          <t>55937</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,04%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,55%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>24650</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>16387</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>29963</t>
+          <t>35373</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>13540</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8121</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>18081</t>
+          <t>19355</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>25,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34140</t>
+          <t>38191</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25881</t>
+          <t>28113</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44598</t>
+          <t>48520</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>17,83%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>197410</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>197410</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>176039</t>
+          <t>197410</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>65708</t>
+          <t>74764</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>65708</t>
+          <t>74764</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>65708</t>
+          <t>74764</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>241747</t>
+          <t>272174</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>241747</t>
+          <t>272174</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>241747</t>
+          <t>272174</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>41815</t>
+          <t>40398</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26168</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>61909</t>
+          <t>59837</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>22888</t>
+          <t>27206</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>19189</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>43456</t>
+          <t>37826</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>64702</t>
+          <t>67604</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>29351</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95822</t>
+          <t>85603</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -2884,32 +2884,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>109153</t>
+          <t>123273</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92870</t>
+          <t>104854</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>129674</t>
+          <t>144873</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2919,32 +2919,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>296841</t>
+          <t>102010</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>149455</t>
+          <t>88187</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>419092</t>
+          <t>117307</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>30,45%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>405994</t>
+          <t>225283</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>251191</t>
+          <t>202449</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>665564</t>
+          <t>248328</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>32,85%</t>
         </is>
       </c>
     </row>
@@ -2997,32 +2997,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>153631</t>
+          <t>159994</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>134675</t>
+          <t>139294</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>176339</t>
+          <t>183127</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3032,32 +3032,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>104686</t>
+          <t>112856</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37641</t>
+          <t>97100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>184942</t>
+          <t>126933</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>35,69%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>258318</t>
+          <t>272850</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>123568</t>
+          <t>249690</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>345122</t>
+          <t>299514</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>36,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>33,03%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>60056</t>
+          <t>69637</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>47390</t>
+          <t>53566</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>76108</t>
+          <t>87118</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>43923</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>35009</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>75734</t>
+          <t>57561</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>100315</t>
+          <t>113561</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>48388</t>
+          <t>95673</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>139208</t>
+          <t>133981</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>17,72%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>42521</t>
+          <t>46514</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>31508</t>
+          <t>34808</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>58561</t>
+          <t>60423</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>26213</t>
+          <t>30209</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>22739</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49197</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>68735</t>
+          <t>76723</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>33429</t>
+          <t>62856</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>94803</t>
+          <t>92846</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -3336,17 +3336,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>407176</t>
+          <t>439817</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>407176</t>
+          <t>439817</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>407176</t>
+          <t>439817</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3371,17 +3371,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>490888</t>
+          <t>316204</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>490888</t>
+          <t>316204</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>490888</t>
+          <t>316204</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>898064</t>
+          <t>756021</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>898064</t>
+          <t>756021</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>898064</t>
+          <t>756021</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3453,32 +3453,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>6892</t>
+          <t>7063</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2517</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>14399</t>
+          <t>13921</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3488,32 +3488,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>22346</t>
+          <t>23919</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>15701</t>
+          <t>17471</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30161</t>
+          <t>33176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>29238</t>
+          <t>30981</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>21725</t>
+          <t>22260</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>41901</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -3566,32 +3566,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>79766</t>
+          <t>103983</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>67248</t>
+          <t>88430</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>94500</t>
+          <t>119558</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>43,08%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>36,32%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>51,04%</t>
+          <t>54,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3601,32 +3601,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>118121</t>
+          <t>137384</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>106494</t>
+          <t>122579</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>133237</t>
+          <t>152076</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>40,7%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>37,26%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>197887</t>
+          <t>241367</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>179574</t>
+          <t>220407</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>217211</t>
+          <t>263381</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>43,93%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>47,93%</t>
         </is>
       </c>
     </row>
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>60913</t>
+          <t>66486</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>48626</t>
+          <t>52451</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>73971</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>23,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3714,32 +3714,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>77356</t>
+          <t>84486</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>65831</t>
+          <t>72348</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>89681</t>
+          <t>98963</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>26,66%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>138270</t>
+          <t>150972</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>120891</t>
+          <t>132021</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>155523</t>
+          <t>169958</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>29,09%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>30,93%</t>
         </is>
       </c>
     </row>
@@ -3792,32 +3792,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>17010</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>10256</t>
+          <t>12514</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>25908</t>
+          <t>31043</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,08%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3827,32 +3827,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>39224</t>
+          <t>44935</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>30365</t>
+          <t>34701</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>56378</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10,46%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>56234</t>
+          <t>64532</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>45226</t>
+          <t>52207</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>69377</t>
+          <t>78676</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,32%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>23410</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>28987</t>
+          <t>34059</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,61%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>33165</t>
+          <t>38222</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>24856</t>
+          <t>29156</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>41774</t>
+          <t>49216</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>53743</t>
+          <t>61632</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>43378</t>
+          <t>48733</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>67069</t>
+          <t>76795</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,98%</t>
         </is>
       </c>
     </row>
@@ -4018,17 +4018,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>185160</t>
+          <t>220540</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>185160</t>
+          <t>220540</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>185160</t>
+          <t>220540</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4053,17 +4053,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>290212</t>
+          <t>328945</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>290212</t>
+          <t>328945</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>290212</t>
+          <t>328945</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>475372</t>
+          <t>549485</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>475372</t>
+          <t>549485</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>475372</t>
+          <t>549485</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -4135,32 +4135,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>21147</t>
+          <t>18346</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>8380</t>
+          <t>7093</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>37317</t>
+          <t>36640</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>9,83%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4170,32 +4170,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>30797</t>
+          <t>32427</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>22193</t>
+          <t>23423</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>43575</t>
+          <t>47015</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4205,32 +4205,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>51944</t>
+          <t>50774</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>35692</t>
+          <t>34705</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>80629</t>
+          <t>72631</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -4248,32 +4248,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>22457</t>
+          <t>24954</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>11448</t>
+          <t>13790</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>36588</t>
+          <t>38405</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>53,24%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4283,32 +4283,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>114344</t>
+          <t>132586</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>99765</t>
+          <t>114770</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>130940</t>
+          <t>151892</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>32,24%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>40,92%</t>
+          <t>42,67%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4318,32 +4318,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>136802</t>
+          <t>157541</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>118770</t>
+          <t>137098</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>158069</t>
+          <t>181958</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>35,31%</t>
+          <t>36,8%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>42,5%</t>
         </is>
       </c>
     </row>
@@ -4361,32 +4361,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>9702</t>
+          <t>10481</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3508</t>
+          <t>3860</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>20675</t>
+          <t>20412</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,53%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>28,3%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4396,32 +4396,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>82943</t>
+          <t>87731</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>68432</t>
+          <t>74444</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>98533</t>
+          <t>102842</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4431,32 +4431,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>92645</t>
+          <t>98212</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>76292</t>
+          <t>83127</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>111347</t>
+          <t>118765</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>27,74%</t>
         </is>
       </c>
     </row>
@@ -4474,32 +4474,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>9174</t>
+          <t>10542</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3616</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>20735</t>
+          <t>23248</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4509,32 +4509,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>41409</t>
+          <t>46087</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>32170</t>
+          <t>36524</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>51816</t>
+          <t>58426</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4544,32 +4544,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>50583</t>
+          <t>56629</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>38280</t>
+          <t>44309</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>64908</t>
+          <t>72906</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,03%</t>
         </is>
       </c>
     </row>
@@ -4587,32 +4587,32 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>4973</t>
+          <t>7812</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>2315</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>14347</t>
+          <t>19508</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>27,04%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4622,32 +4622,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>50512</t>
+          <t>57133</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>39531</t>
+          <t>44605</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>63427</t>
+          <t>71393</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,53%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4657,32 +4657,32 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>55485</t>
+          <t>64945</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>43680</t>
+          <t>49058</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>70245</t>
+          <t>82543</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,28%</t>
         </is>
       </c>
     </row>
@@ -4700,17 +4700,17 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>72135</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>72135</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>67454</t>
+          <t>72135</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4735,17 +4735,17 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>320005</t>
+          <t>355965</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>320005</t>
+          <t>355965</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>320005</t>
+          <t>355965</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4770,17 +4770,17 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>387459</t>
+          <t>428101</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>387459</t>
+          <t>428101</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>387459</t>
+          <t>428101</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4817,32 +4817,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>114739</t>
+          <t>110307</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>89258</t>
+          <t>87361</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>151425</t>
+          <t>140073</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4852,32 +4852,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>102572</t>
+          <t>114345</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>63160</t>
+          <t>94961</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>127839</t>
+          <t>133711</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4887,32 +4887,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>217310</t>
+          <t>224652</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>166661</t>
+          <t>195129</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>259165</t>
+          <t>258975</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,65%</t>
         </is>
       </c>
     </row>
@@ -4930,32 +4930,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>280630</t>
+          <t>331582</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>247667</t>
+          <t>299285</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>309400</t>
+          <t>368172</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,56%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4965,32 +4965,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>580396</t>
+          <t>430569</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>428221</t>
+          <t>399977</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>905518</t>
+          <t>464715</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5000,32 +5000,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>861025</t>
+          <t>762151</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>696176</t>
+          <t>713518</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1288960</t>
+          <t>805291</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>30,01%</t>
         </is>
       </c>
     </row>
@@ -5043,32 +5043,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>464986</t>
+          <t>493966</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>429440</t>
+          <t>454613</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>502960</t>
+          <t>532912</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>38,07%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>41,07%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5078,32 +5078,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>414409</t>
+          <t>446221</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>267973</t>
+          <t>417671</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>490885</t>
+          <t>476060</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>28,57%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>33,84%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5113,32 +5113,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>879395</t>
+          <t>940187</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>661342</t>
+          <t>892912</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>970404</t>
+          <t>987074</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>35,04%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>36,8%</t>
+          <t>36,78%</t>
         </is>
       </c>
     </row>
@@ -5156,32 +5156,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>190062</t>
+          <t>209318</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>165392</t>
+          <t>183243</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>218665</t>
+          <t>239226</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5191,32 +5191,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>185708</t>
+          <t>205142</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>103689</t>
+          <t>181503</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>223399</t>
+          <t>229078</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5226,32 +5226,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>375770</t>
+          <t>414460</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>300443</t>
+          <t>379823</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>423671</t>
+          <t>449858</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -5269,32 +5269,32 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>135793</t>
+          <t>152259</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>117249</t>
+          <t>127917</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>161396</t>
+          <t>176293</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
@@ -5304,32 +5304,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>167609</t>
+          <t>189719</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>102279</t>
+          <t>169400</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>202776</t>
+          <t>215404</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5339,32 +5339,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>303403</t>
+          <t>341978</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>233733</t>
+          <t>309245</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>342775</t>
+          <t>376029</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -5382,17 +5382,17 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>1186210</t>
+          <t>1297432</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>1186210</t>
+          <t>1297432</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1186210</t>
+          <t>1297432</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5417,17 +5417,17 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>1450694</t>
+          <t>1385997</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>1450694</t>
+          <t>1385997</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>1450694</t>
+          <t>1385997</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5452,17 +5452,17 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>2636903</t>
+          <t>2683429</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>2636903</t>
+          <t>2683429</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>2636903</t>
+          <t>2683429</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
